--- a/outputs/daily/hr_rankings_2026-10-01.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-01.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>62.6</v>
+        <v>63.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Sheet Consensus</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Sheet Consensus</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -891,7 +891,7 @@
         <v>48.4</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -907,39 +907,35 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1084,7 +1080,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1200,12 +1196,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1224,7 +1220,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59</v>
+        <v>59.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1238,7 +1234,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1251,7 +1247,7 @@
         <v>48.4</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1267,39 +1263,35 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1444,7 +1436,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1540,7 +1532,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ronald Acuna</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1550,7 +1542,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1560,7 +1552,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1584,7 +1576,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>57.3</v>
+        <v>59.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1598,7 +1590,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1611,7 +1603,7 @@
         <v>48.4</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1620,46 +1612,40 @@
         <v>53.3</v>
       </c>
       <c r="V4" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="W4" t="n">
         <v>50</v>
       </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1804,7 +1790,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1838,56 +1824,16 @@
         </is>
       </c>
       <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>0.041</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>EV helps but ISO not HR-friendly today</t>
-        </is>
-      </c>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr"/>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1900,7 +1846,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1920,12 +1866,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1944,7 +1890,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>54.3</v>
+        <v>55.1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1958,7 +1904,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1971,7 +1917,7 @@
         <v>48.4</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1987,39 +1933,35 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2164,7 +2106,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2280,7 +2222,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2304,7 +2246,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>54.2</v>
+        <v>54.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2318,7 +2260,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -2331,7 +2273,7 @@
         <v>48.4</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
@@ -2347,39 +2289,35 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2524,7 +2462,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2640,12 +2578,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2664,7 +2602,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>48.6</v>
+        <v>50.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2678,7 +2616,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2691,7 +2629,7 @@
         <v>48.4</v>
       </c>
       <c r="S7" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
@@ -2707,39 +2645,35 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2884,7 +2818,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2975,24 +2909,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>547180</t>
+          <t>573262</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bryce Harper</t>
+          <t>Mike Yastrzemski</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -3000,31 +2934,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>48.2</v>
+        <v>49.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -3038,71 +2972,65 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>49</v>
+        <v>34.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>47.8</v>
       </c>
       <c r="R8" t="n">
         <v>48.4</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T8" t="n">
+        <v>80</v>
+      </c>
+      <c r="U8" t="n">
+        <v>24</v>
+      </c>
+      <c r="V8" t="n">
         <v>50</v>
       </c>
-      <c r="U8" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="V8" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="W8" t="n">
-        <v>83</v>
-      </c>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr"/>
@@ -3119,12 +3047,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -3134,12 +3062,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 1 HR</t>
+          <t>Last 7 games: 3/19, 1 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -3149,102 +3077,102 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>44.21</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>90.39</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>101.6293</t>
+          <t>99.7248</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4843</t>
+          <t>0.3833</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.2142</t>
+          <t>0.1477</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3757</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>38.47</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>30.91</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>0.1602</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3278,56 +3206,16 @@
         </is>
       </c>
       <c r="BP8" t="inlineStr"/>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>16.5</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>0.424</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>4.88</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>Elite hitter/sheet power; pitcher split less targetable</t>
-        </is>
-      </c>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3335,22 +3223,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>573262</t>
+          <t>547180</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mike Yastrzemski</t>
+          <t>Bryce Harper</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3360,31 +3248,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>47</v>
+        <v>48.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3398,69 +3286,67 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>34.7</v>
+        <v>49</v>
       </c>
       <c r="Q9" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R9" t="n">
         <v>48.4</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>24</v>
+        <v>32.5</v>
       </c>
       <c r="V9" t="n">
-        <v>50</v>
-      </c>
-      <c r="W9" t="inlineStr"/>
+        <v>62.9</v>
+      </c>
+      <c r="W9" t="n">
+        <v>83</v>
+      </c>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr"/>
@@ -3477,12 +3363,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -3492,12 +3378,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 1 HR</t>
+          <t>Last 7 games: 6/28, 1 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -3507,102 +3393,102 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>44.21</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.39</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>99.7248</t>
+          <t>101.6293</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3833</t>
+          <t>0.4843</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1477</t>
+          <t>0.2142</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3757</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>38.47</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.219</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3636,16 +3522,56 @@
         </is>
       </c>
       <c r="BP9" t="inlineStr"/>
-      <c r="BQ9" t="inlineStr"/>
-      <c r="BR9" t="inlineStr"/>
-      <c r="BS9" t="inlineStr"/>
-      <c r="BT9" t="inlineStr"/>
-      <c r="BU9" t="inlineStr"/>
-      <c r="BV9" t="inlineStr"/>
-      <c r="BW9" t="inlineStr"/>
-      <c r="BX9" t="inlineStr"/>
-      <c r="BY9" t="inlineStr"/>
-      <c r="BZ9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>16.5</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>0.424</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>Elite hitter/sheet power; pitcher split less targetable</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3678,12 +3604,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3702,7 +3628,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>42.3</v>
+        <v>44.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3716,7 +3642,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3729,7 +3655,7 @@
         <v>48.4</v>
       </c>
       <c r="S10" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>78</v>
@@ -3743,39 +3669,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3920,7 +3842,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3996,7 +3918,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4020,7 +3942,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>41.8</v>
+        <v>42.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -4034,7 +3956,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -4047,7 +3969,7 @@
         <v>48.4</v>
       </c>
       <c r="S11" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
         <v>78</v>
@@ -4061,39 +3983,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4238,7 +4156,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -4289,24 +4207,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>624641</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Edmundo Sosa</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -4314,31 +4232,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>41.4</v>
+        <v>42.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4352,26 +4270,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>30.1</v>
+        <v>10.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>20</v>
+        <v>47.8</v>
       </c>
       <c r="R12" t="n">
         <v>48.4</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>71.59999999999999</v>
+        <v>50.3</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -4379,42 +4297,38 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -4431,27 +4345,27 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -4461,102 +4375,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>38.84</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>87.77</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>99.9033</t>
+          <t>96.2638</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.4281</t>
+          <t>0.3618</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.1614</t>
+          <t>0.1008</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3166</t>
+          <t>0.2962</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>72.44</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>31.89</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>21.78</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.1853</t>
+          <t>0.1203</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4607,24 +4521,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>624641</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Edmundo Sosa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -4632,31 +4546,31 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>41.4</v>
+        <v>42</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4670,26 +4584,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.2</v>
+        <v>30.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R13" t="n">
         <v>48.4</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>50.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4697,42 +4611,38 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr"/>
@@ -4749,27 +4659,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4779,102 +4689,102 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>38.84</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>96.2638</t>
+          <t>99.9033</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3618</t>
+          <t>0.4281</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.1008</t>
+          <t>0.1614</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2962</t>
+          <t>0.3166</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>72.44</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>21.78</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1203</t>
+          <t>0.1853</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4925,24 +4835,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>669016</t>
+          <t>642086</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brandon Marsh</t>
+          <t>Dominic Smith</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -4950,31 +4860,31 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>40.9</v>
+        <v>40.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4988,26 +4898,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>36.1</v>
+        <v>21.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>20</v>
+        <v>47.8</v>
       </c>
       <c r="R14" t="n">
         <v>48.4</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>35.6</v>
+        <v>18.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -5015,42 +4925,38 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
@@ -5067,12 +4973,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -5082,12 +4988,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 1 HR</t>
+          <t>Last 7 games: 1/11, 1 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -5097,102 +5003,102 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>33.47</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>89.77</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>100.0232</t>
+          <t>97.8111</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.4103</t>
+          <t>0.384</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.1564</t>
+          <t>0.1401</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>28.68</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1525</t>
+          <t>0.1309</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -5243,24 +5149,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>681082</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -5268,31 +5174,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>40.9</v>
+        <v>39.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5306,26 +5212,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>15.3</v>
+        <v>25.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>47.3</v>
+        <v>20</v>
       </c>
       <c r="R15" t="n">
         <v>48.4</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>40.7</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -5333,42 +5239,38 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr"/>
@@ -5385,12 +5287,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -5400,12 +5302,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Contact streak: 9/23 over last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -5415,102 +5317,102 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>35.24</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>96.687</t>
+          <t>98.4048</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1184</t>
+          <t>0.1383</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2808</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5561,24 +5463,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>669221</t>
+          <t>650559</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sean Murphy</t>
+          <t>Bryan De La Cruz</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -5586,31 +5488,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>40.6</v>
+        <v>38.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5624,26 +5526,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>34</v>
+        <v>24.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R16" t="n">
         <v>48.4</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5651,42 +5553,38 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -5703,12 +5601,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -5718,12 +5616,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Last 7 games: 2/17, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5733,102 +5631,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>88.19</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>101.2803</t>
+          <t>99.8033</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3548</t>
+          <t>0.3346</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2853</t>
+          <t>0.2828</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>70.92</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>16.37</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>25.37</t>
+          <t>19.87</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1456</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5879,24 +5777,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>681082</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -5904,31 +5802,31 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>40.4</v>
+        <v>38.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5942,26 +5840,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>25.2</v>
+        <v>15.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>47.3</v>
       </c>
       <c r="R17" t="n">
         <v>48.4</v>
       </c>
       <c r="S17" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U17" t="n">
-        <v>40.7</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5969,42 +5867,38 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -6021,12 +5915,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -6036,12 +5930,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Contact streak: 9/23 over last 7 games</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -6051,102 +5945,102 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>98.4048</t>
+          <t>96.687</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.1383</t>
+          <t>0.1184</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.2808</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -6222,12 +6116,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -6246,7 +6140,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>35.7</v>
+        <v>37.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -6260,7 +6154,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -6273,7 +6167,7 @@
         <v>48.4</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
         <v>78</v>
@@ -6287,39 +6181,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -6464,7 +6354,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6540,12 +6430,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -6564,7 +6454,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28.8</v>
+        <v>28.4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6578,7 +6468,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -6591,7 +6481,7 @@
         <v>48.4</v>
       </c>
       <c r="S19" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>50</v>
@@ -6605,39 +6495,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -6782,7 +6668,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -7264,7 +7150,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7288,7 +7174,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>62.6</v>
+        <v>63.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7302,7 +7188,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Sheet Consensus</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Sheet Consensus</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -7315,7 +7201,7 @@
         <v>48.4</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -7331,39 +7217,35 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7508,7 +7390,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7624,12 +7506,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -7648,7 +7530,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59</v>
+        <v>59.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7662,7 +7544,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -7675,7 +7557,7 @@
         <v>48.4</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -7691,39 +7573,35 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7868,7 +7746,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7964,7 +7842,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ronald Acuna</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -7974,7 +7852,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -7984,7 +7862,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -8008,7 +7886,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>57.3</v>
+        <v>59.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -8022,7 +7900,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -8035,7 +7913,7 @@
         <v>48.4</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -8044,46 +7922,40 @@
         <v>53.3</v>
       </c>
       <c r="V4" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="W4" t="n">
         <v>50</v>
       </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8228,7 +8100,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -8262,56 +8134,16 @@
         </is>
       </c>
       <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>0.041</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>EV helps but ISO not HR-friendly today</t>
-        </is>
-      </c>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr"/>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -8324,7 +8156,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -8344,12 +8176,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -8368,7 +8200,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>54.3</v>
+        <v>55.1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -8382,7 +8214,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -8395,7 +8227,7 @@
         <v>48.4</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -8411,39 +8243,35 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8588,7 +8416,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8704,7 +8532,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8728,7 +8556,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>54.2</v>
+        <v>54.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8742,7 +8570,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -8755,7 +8583,7 @@
         <v>48.4</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
@@ -8771,39 +8599,35 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -8948,7 +8772,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -9064,12 +8888,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -9088,7 +8912,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>48.6</v>
+        <v>50.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -9102,7 +8926,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -9115,7 +8939,7 @@
         <v>48.4</v>
       </c>
       <c r="S7" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
@@ -9131,39 +8955,35 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9308,7 +9128,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -9399,24 +9219,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>547180</t>
+          <t>573262</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bryce Harper</t>
+          <t>Mike Yastrzemski</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -9424,31 +9244,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>48.2</v>
+        <v>49.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -9462,71 +9282,65 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>49</v>
+        <v>34.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>47.8</v>
       </c>
       <c r="R8" t="n">
         <v>48.4</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T8" t="n">
+        <v>80</v>
+      </c>
+      <c r="U8" t="n">
+        <v>24</v>
+      </c>
+      <c r="V8" t="n">
         <v>50</v>
       </c>
-      <c r="U8" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="V8" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="W8" t="n">
-        <v>83</v>
-      </c>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr"/>
@@ -9543,12 +9357,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -9558,12 +9372,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 1 HR</t>
+          <t>Last 7 games: 3/19, 1 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -9573,102 +9387,102 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>44.21</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>90.39</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>101.6293</t>
+          <t>99.7248</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4843</t>
+          <t>0.3833</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.2142</t>
+          <t>0.1477</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3757</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>38.47</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>30.91</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>0.1602</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9702,56 +9516,16 @@
         </is>
       </c>
       <c r="BP8" t="inlineStr"/>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>16.5</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>0.424</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>4.88</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>Elite hitter/sheet power; pitcher split less targetable</t>
-        </is>
-      </c>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -9759,22 +9533,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>573262</t>
+          <t>547180</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mike Yastrzemski</t>
+          <t>Bryce Harper</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -9784,31 +9558,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>47</v>
+        <v>48.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9822,69 +9596,67 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>34.7</v>
+        <v>49</v>
       </c>
       <c r="Q9" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R9" t="n">
         <v>48.4</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>24</v>
+        <v>32.5</v>
       </c>
       <c r="V9" t="n">
-        <v>50</v>
-      </c>
-      <c r="W9" t="inlineStr"/>
+        <v>62.9</v>
+      </c>
+      <c r="W9" t="n">
+        <v>83</v>
+      </c>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr"/>
@@ -9901,12 +9673,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -9916,12 +9688,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 1 HR</t>
+          <t>Last 7 games: 6/28, 1 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -9931,102 +9703,102 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>44.21</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.39</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>99.7248</t>
+          <t>101.6293</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3833</t>
+          <t>0.4843</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1477</t>
+          <t>0.2142</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3757</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>38.47</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.219</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -10060,16 +9832,56 @@
         </is>
       </c>
       <c r="BP9" t="inlineStr"/>
-      <c r="BQ9" t="inlineStr"/>
-      <c r="BR9" t="inlineStr"/>
-      <c r="BS9" t="inlineStr"/>
-      <c r="BT9" t="inlineStr"/>
-      <c r="BU9" t="inlineStr"/>
-      <c r="BV9" t="inlineStr"/>
-      <c r="BW9" t="inlineStr"/>
-      <c r="BX9" t="inlineStr"/>
-      <c r="BY9" t="inlineStr"/>
-      <c r="BZ9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>16.5</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>0.424</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>Elite hitter/sheet power; pitcher split less targetable</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -10102,12 +9914,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -10126,7 +9938,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>42.3</v>
+        <v>44.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -10140,7 +9952,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -10153,7 +9965,7 @@
         <v>48.4</v>
       </c>
       <c r="S10" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>78</v>
@@ -10167,39 +9979,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10344,7 +10152,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -10420,7 +10228,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -10444,7 +10252,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>41.8</v>
+        <v>42.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -10458,7 +10266,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -10471,7 +10279,7 @@
         <v>48.4</v>
       </c>
       <c r="S11" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
         <v>78</v>
@@ -10485,39 +10293,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10662,7 +10466,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10713,24 +10517,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>624641</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Edmundo Sosa</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -10738,31 +10542,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>41.4</v>
+        <v>42.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10776,26 +10580,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>30.1</v>
+        <v>10.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>20</v>
+        <v>47.8</v>
       </c>
       <c r="R12" t="n">
         <v>48.4</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>71.59999999999999</v>
+        <v>50.3</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -10803,42 +10607,38 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -10855,27 +10655,27 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -10885,102 +10685,102 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>38.84</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>87.77</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>99.9033</t>
+          <t>96.2638</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.4281</t>
+          <t>0.3618</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.1614</t>
+          <t>0.1008</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3166</t>
+          <t>0.2962</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>72.44</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>31.89</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>21.78</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.1853</t>
+          <t>0.1203</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -11031,24 +10831,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>624641</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Edmundo Sosa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -11056,31 +10856,31 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>41.4</v>
+        <v>42</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -11094,26 +10894,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.2</v>
+        <v>30.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R13" t="n">
         <v>48.4</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>50.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -11121,42 +10921,38 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr"/>
@@ -11173,27 +10969,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -11203,102 +10999,102 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>38.84</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>96.2638</t>
+          <t>99.9033</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3618</t>
+          <t>0.4281</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.1008</t>
+          <t>0.1614</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2962</t>
+          <t>0.3166</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>72.44</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>21.78</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1203</t>
+          <t>0.1853</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -11349,24 +11145,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>669016</t>
+          <t>642086</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brandon Marsh</t>
+          <t>Dominic Smith</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -11374,31 +11170,31 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>40.9</v>
+        <v>40.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -11412,26 +11208,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>36.1</v>
+        <v>21.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>20</v>
+        <v>47.8</v>
       </c>
       <c r="R14" t="n">
         <v>48.4</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>35.6</v>
+        <v>18.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -11439,42 +11235,38 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
@@ -11491,12 +11283,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -11506,12 +11298,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 1 HR</t>
+          <t>Last 7 games: 1/11, 1 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -11521,102 +11313,102 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>33.47</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>89.77</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>100.0232</t>
+          <t>97.8111</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.4103</t>
+          <t>0.384</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.1564</t>
+          <t>0.1401</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>28.68</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1525</t>
+          <t>0.1309</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11667,24 +11459,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>681082</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -11692,31 +11484,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>40.9</v>
+        <v>39.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11730,26 +11522,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>15.3</v>
+        <v>25.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>47.3</v>
+        <v>20</v>
       </c>
       <c r="R15" t="n">
         <v>48.4</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>40.7</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -11757,42 +11549,38 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr"/>
@@ -11809,12 +11597,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -11824,12 +11612,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Contact streak: 9/23 over last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -11839,102 +11627,102 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>35.24</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>96.687</t>
+          <t>98.4048</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1184</t>
+          <t>0.1383</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2808</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11985,24 +11773,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>669221</t>
+          <t>650559</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sean Murphy</t>
+          <t>Bryan De La Cruz</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -12010,31 +11798,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Ray Kerr</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>678061</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>40.6</v>
+        <v>38.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -12048,26 +11836,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>34</v>
+        <v>24.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>47.8</v>
+        <v>20</v>
       </c>
       <c r="R16" t="n">
         <v>48.4</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -12075,42 +11863,38 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -12127,12 +11911,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -12142,12 +11926,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Last 7 games: 2/17, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -12157,102 +11941,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>88.19</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>101.2803</t>
+          <t>99.8033</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3548</t>
+          <t>0.3346</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2853</t>
+          <t>0.2828</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>70.92</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>16.37</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>25.37</t>
+          <t>19.87</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1456</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.4184</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -12303,24 +12087,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>681082</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-02T00:00:00Z</t>
@@ -12328,31 +12112,31 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Ray Kerr</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>678061</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>40.4</v>
+        <v>38.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -12366,26 +12150,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>25.2</v>
+        <v>15.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>47.3</v>
       </c>
       <c r="R17" t="n">
         <v>48.4</v>
       </c>
       <c r="S17" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U17" t="n">
-        <v>40.7</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -12393,42 +12177,38 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -12445,12 +12225,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -12460,12 +12240,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Contact streak: 9/23 over last 7 games</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.9% barrel, 2.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.2% barrel, 31.3 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -12475,102 +12255,102 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>98.4048</t>
+          <t>96.687</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.1383</t>
+          <t>0.1184</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.2808</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4184</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12646,12 +12426,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -12670,7 +12450,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>35.7</v>
+        <v>37.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12684,7 +12464,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -12697,7 +12477,7 @@
         <v>48.4</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
         <v>78</v>
@@ -12711,39 +12491,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -12888,7 +12664,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12964,12 +12740,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -12988,7 +12764,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28.8</v>
+        <v>28.4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -13002,7 +12778,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -13015,7 +12791,7 @@
         <v>48.4</v>
       </c>
       <c r="S19" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>50</v>
@@ -13029,39 +12805,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -13206,7 +12978,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>345 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-01.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-01.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -11484,7 +11484,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11798,7 +11798,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -12112,7 +12112,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
